--- a/docs/02_技术领域×新闻类型评分规则表.xlsx
+++ b/docs/02_技术领域×新闻类型评分规则表.xlsx
@@ -7320,7 +7320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7344,6 +7344,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -7486,6 +7487,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
@@ -7682,6 +7684,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
@@ -7771,183 +7774,338 @@
       <c r="D26" s="8" t="inlineStr"/>
       <c r="E26" s="8" t="inlineStr"/>
     </row>
+    <row r="27"/>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>四、25 类新闻一级分类 → 大类映射（两本工作簿分类体系对齐）</t>
-        </is>
-      </c>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>四、展示链路映射（v1.09 2026-09-24 依据《新闻类型展示分类.xlsx》修订：论文单列＋新闻两级结构）</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>新闻一级分类</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>v1.09 修订：① 论文（T01）从原『科研与知识资产』独立为『论文』展示大类，小类=四分型（综述/研究型/分析型/新闻·评论·观点）；② 其余 7 组为『新闻』展示大类的小类；③ 管线 v1.09 起 semantic_results 增输出 展示大类/展示小类/归入大类 三字段，看板主榜/参考区/明细均带展示分类列——纯展示标注，不影响 S1–S10 评分/档位/优先级（用户 2026-09-24 口径）。</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>展示大类</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>展示小类</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>归入大类</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>涉及 T 类</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr"/>
-      <c r="E29" s="6" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>科研与知识资产</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="E30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>论文</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>综述</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>T01 论文（四分型）/T02 报告/T03 专利/T04 软著/T06 第三方测试；T05 科研项目用 card_project 计分（B链3），展示归 A</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr"/>
-      <c r="E30" s="7" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>T01 论文（四分型）</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>论文</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>研究型</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>T01 论文（四分型）</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>论文</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>分析类</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>T01 论文（四分型）</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>论文</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>新闻/评论/观点</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>T01 论文（四分型）</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>新闻</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>知识资产</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>T02 报告/T03 专利/T04 软著/T06 第三方测试；T05 科研项目用 card_project 计分（B链3），展示归 A</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>新闻</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
         <is>
           <t>工程与产业化</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>B（链2-5）</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>T07 工程验证/T08 项目设施/T09 产品装备/T10 生产运行</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr"/>
-      <c r="E31" s="8" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="E36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>新闻</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
         <is>
           <t>企业经营、合作与资本</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>T11 企业经营/T12 企业合作/T13 投融资/T14 并购</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr"/>
-      <c r="E32" s="7" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="E37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>新闻</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
         <is>
           <t>资源、市场与产业链</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>C + D + B链6</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>T15 资源→C（卡待建）；T16 市场贸易→D；T17 供应链→B链6/C；T18 采购→C</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr"/>
-      <c r="E33" s="8" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="E38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>新闻</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
         <is>
           <t>政策、法规与标准</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>T19 政策战略/T20 法规标准认证</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr"/>
-      <c r="E34" s="7" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="E39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>新闻</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
         <is>
           <t>人才与组织动态</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>T21</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr"/>
-      <c r="E35" s="8" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="E40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>新闻</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>观点与交流</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>A（观点评论）</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>T22 观点访谈→A；T23 深度分析→A（建模分析通道）；T24 会议→场合标签，发布物按实质归类</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr"/>
-      <c r="E36" s="7" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="E41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>待定/信息不足</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
         <is>
           <t>T25 兜底，不参与展示分组</t>
         </is>
       </c>
-      <c r="D37" s="8" t="inlineStr"/>
-      <c r="E37" s="8" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>（映射口径）T01 四分型由 cls_data 分型线索在评分卡内起作用；展示层按 T01 整体标『论文·四分型』，逐条分型不在展示层展开。域外记录展示字段=『—/域外/—』。本节与《新闻类型展示分类.xlsx》单源对齐，后续修订以该表为准同步。</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/docs/02_技术领域×新闻类型评分规则表.xlsx
+++ b/docs/02_技术领域×新闻类型评分规则表.xlsx
@@ -8099,7 +8099,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>（映射口径）T01 四分型由 cls_data 分型线索在评分卡内起作用；展示层按 T01 整体标『论文·四分型』，逐条分型不在展示层展开。域外记录展示字段=『—/域外/—』。本节与《新闻类型展示分类.xlsx》单源对齐，后续修订以该表为准同步。</t>
+          <t>（映射口径）T01 四分型逐条判定（用户 2026-09-24 追加口径：四小类不混标）——题名综述词（综述/review/perspective/survey/meta-analysis 等）→综述；题名评估分析词（技术经济/生命周期/碳足迹/情景/assessment/techno-economic/LCA 等）→分析类；非文献源（媒体解读/转载报道稿，全文转载特征除外）→新闻/评论/观点；默认研究型。stats 增 paperSubtypes 四类计数。域外记录展示字段=『—/域外/—』。本节与《新闻类型展示分类.xlsx》单源对齐，后续修订以该表为准同步。</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
